--- a/DTY May26產銷260502-1400+500+30_clear.xlsx
+++ b/DTY May26產銷260502-1400+500+30_clear.xlsx
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>FD2F6TG2K like</t>
+          <t>FD2F6IA2K</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>FP82170R(L56</t>
+          <t>FP82170R(L56&gt;82173R</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>0</v>
+        <v>18.48</v>
       </c>
       <c r="L82" s="4" t="n">
         <v>75</v>
@@ -6012,13 +6012,13 @@
         <v>75</v>
       </c>
       <c r="U82" s="4" t="n">
-        <v>0</v>
+        <v>18.48</v>
       </c>
       <c r="V82" s="4" t="inlineStr"/>
       <c r="W82" s="4" t="inlineStr"/>
       <c r="X82" s="4" t="inlineStr">
         <is>
-          <t>2F6TG2 LIKE</t>
+          <t>2F6IA2</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>FD2F7D93K like</t>
+          <t>FD2F7E03K</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -6050,11 +6050,11 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>4/15-5/10X</t>
+          <t>4/15-5/16X</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>3.2</v>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>32</v>
+        <v>51.2</v>
       </c>
       <c r="M83" s="4" t="inlineStr"/>
       <c r="N83" s="4" t="inlineStr"/>
@@ -6088,13 +6088,13 @@
         <v>10</v>
       </c>
       <c r="U83" s="4" t="n">
-        <v>22</v>
+        <v>45.82</v>
       </c>
       <c r="V83" s="4" t="inlineStr"/>
       <c r="W83" s="4" t="inlineStr"/>
       <c r="X83" s="4" t="inlineStr">
         <is>
-          <t>2F7D93 LIKE</t>
+          <t>2F7E03</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>FD2F6TG2K like</t>
+          <t>FD2F6GT2K like</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -6122,18 +6122,18 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>5/11/31</t>
+          <t>5/17/31</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>FP82170R(L56</t>
+          <t>FP82173R(L56</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>50</v>
+        <v>47.5</v>
       </c>
       <c r="M84" s="4" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr"/>
@@ -6160,13 +6160,13 @@
         <v>50</v>
       </c>
       <c r="U84" s="4" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="V84" s="4" t="inlineStr"/>
       <c r="W84" s="4" t="inlineStr"/>
       <c r="X84" s="4" t="inlineStr">
         <is>
-          <t>2F6TG2 LIKE</t>
+          <t>2F6GT2 LIKE</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>FD2F6TG2K</t>
+          <t>FD2F6GT2K</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0</v>
+        <v>50.985</v>
       </c>
       <c r="L87" s="4" t="n">
         <v>150</v>
@@ -6380,13 +6380,13 @@
         <v>150</v>
       </c>
       <c r="U87" s="4" t="n">
-        <v>0</v>
+        <v>50.98500000000001</v>
       </c>
       <c r="V87" s="4" t="inlineStr"/>
       <c r="W87" s="4" t="inlineStr"/>
       <c r="X87" s="4" t="inlineStr">
         <is>
-          <t>2F6TG2</t>
+          <t>2F6GT2</t>
         </is>
       </c>
     </row>
